--- a/outputs/製品DEG色相悪化_事実整理.xlsx
+++ b/outputs/製品DEG色相悪化_事実整理.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="事実の整理" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="推定メカニズム" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別マトリクス" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="発生事象・着色物質" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="なぜ今回起きたか" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設備の関与・開放" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設備・開放" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="対応" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品質管理・残論点" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,19 +33,18 @@
     <font>
       <name val="游ゴシック"/>
       <b val="1"/>
-      <color rgb="001F3864"/>
+      <color rgb="00005BAB"/>
       <sz val="13"/>
     </font>
     <font>
       <name val="游ゴシック"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <color rgb="00555555"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <name val="游ゴシック"/>
       <b val="1"/>
-      <color rgb="00222222"/>
+      <color rgb="00003F7E"/>
       <sz val="10.5"/>
     </font>
     <font>
@@ -56,22 +55,28 @@
     <font>
       <name val="游ゴシック"/>
       <b val="1"/>
-      <color rgb="001F3864"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <color rgb="00555555"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <color rgb="00005BAB"/>
       <sz val="10.5"/>
     </font>
     <font>
       <name val="游ゴシック"/>
       <b val="1"/>
-      <color rgb="001F3864"/>
+      <color rgb="00005BAB"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="游ゴシック"/>
-      <color rgb="00555555"/>
-      <sz val="9.5"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -80,26 +85,41 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
+        <fgColor rgb="00D7E0E5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00E8F1E5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAEFF7"/>
+        <fgColor rgb="00FBF1DC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00E9F0F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCE6EF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00005BAB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBEFF2"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -109,23 +129,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00C9D2D8"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00C9D2D8"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00C9D2D8"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00C9D2D8"/>
       </bottom>
     </border>
     <border>
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00C9D2D8"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -133,24 +153,35 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00C9D2D8"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00C9D2D8"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C9D2D8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9D2D8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00C9D2D8"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00C9D2D8"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00C9D2D8"/>
       </bottom>
       <diagonal/>
     </border>
@@ -158,44 +189,69 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -562,133 +618,233 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="96" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>製品DEG色相悪化　事実の整理</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
+          <t>製品DEG色相悪化　工程別の事実整理　→　1本の筋（仮説）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>発生事象（事実）</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>冬定修後の再稼働（3月）以降、製品DEGがタンク保管中に色相（APHA）を経時上昇。約1か月半で検査規格を超過（APHA&lt;5 → 25〜35）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="3" t="inlineStr"/>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>プラント出口（ストリーム品）は常に規格内（APHA&lt;5）。タンク（窒素封入）で保管中にのみ上昇する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="3" t="inlineStr"/>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>同じ製品でも、ドラム充填品・SP転送品（大気接触）では色相上昇しない。共配ライン残液（27日保管）も悪化なし。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="3" t="inlineStr"/>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>色相・外観以外の品質規格（純度・MEG/TEG・水分・金属・蒸留性状）は実測で正常品の範囲内。pHのみ通常より僅かに高め（+0.1〜0.2程度）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>着色物質・現象（事実）</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>UVスペクトルで300nm付近と450nm付近に吸収。色相（APHA）上昇に伴い450nmが増大（450nmの補色＝黄、観測色と一致）。APHA30以上で550〜650nmにも吸収。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="3" t="inlineStr"/>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>450nm吸光度とAPHAが相関。GPCで分子量200〜800の分布。GCの複数検体が457nmを捕捉。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="3" t="inlineStr"/>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>T-555残液は5/18時点（APHA30）以降、APHAが上昇していない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="3" t="inlineStr"/>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>アルデヒド類（A-ALD・F-ALD・アクロレイン）も検出されるが、アクロレイン濃度とAPHAは相関しない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>着色物質（推定）</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>着色物質は共役ポリエン（CH=CHの連なり）を持つ化合物の混合物と推定。共役が伸びるほど吸収が長波長化し、十分に伸びると可視域450nm（黄）に達する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="3" t="inlineStr"/>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>GPCの200〜800という幅は単一物質でなくオリゴマー混合物を示す（数平均の分子量はおよそ280〜300、上限側はオリゴマー化やグリコール付加で大きくなる）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="3" t="inlineStr"/>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>存在量はUV吸光度からの換算で数ppb〜10ppb程度（ppbオーダー、絶対定量は未確立）。共役系の吸光係数が極めて大きいため、この微量で色がつく。</t>
-        </is>
-      </c>
+          <t>各工程で：①運転で見えた事実　②RDで検証した事実　③文献・この工程で起こる反応　→　④この工程の筋。全工程をトータルすると下段の1本の筋になる。</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>工程</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>① 運転で見えた事実（運転・解放結果）</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>② RDで検証した事実（分析・ベンチ）</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>③ 文献・原理（この工程で起こる反応）</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>④ この工程の筋</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="92" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>EO反応器
+(R-1101)</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>原料EO中A-ALD/EO=0.78kg/t（過去実績の上位、通常0.11〜0.35）。F-ALDも増加。製品出口は規格内。</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>ラボでF/A-ALD添加→反応器出口相当でUV220/260が上昇。反応器で生じたUV成分はほぼそのまま後段へ持ち越す。</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>触媒選択性低下でアルデヒド類が副生増。アルデヒドはアルドール縮合・着色の出発物質。</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>種となるアルデヒドが増えた＝着色の起点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="92" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>脱水塔まわり
+(C-1404)</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>脱水塔ボトムは低水分（修理後10ppm台）。※MEG塔リボイラーの穴で従来は50ppm台と誤認、修理後に低下。</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>水分があると縮合は進みにくい（脱水反応）。水分の効きは感度2〜3割の見立て。</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>アルドール縮合は脱水を伴う平衡。低水分ほど縮合（脱水）側へ寄る。</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>低水分が縮合を後押しする条件。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="92" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>MEG塔／リサイクル塔
+(C-1501/C-1502)</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>C-1502トップでA-ALDが一時的に異常高（3〜7ppm、過去1ppm以下）。脱水塔BTM・C-1501BTMは過去同水準。開放で異常な汚れ・活性金属なし（CS→SUS改造部も錆込みなし）。</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>物質収支上はC-1502でALD生成に見えるが、重質側で生じた縮合体が軽質ゆえ蒸留で上に運ばれた塔間循環で説明（検出位置≠生成位置）。</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>重質化した縮合体は蒸留系を循環し、一部はレトロ的に分解してALDに見える。</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>MEG系は着色の場ではない（活性金属なし）。縮合体が系内を回りDEG留分へ向かう通過点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="92" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>DEG塔
+(C-1503)</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>C-1503トップに黒色付着物（XRFでほぼ鉄＝サビ）。水抽出でギ酸70ppm・グリコール酸12ppmを検出。</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>付着物をDEGに共存させてもλmax380nmのみで450nmは再現せず。蒸留DEGの短時間保管でも450nmは出ない。</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>塩基・高温下でアルドール縮合が進み、共役の短い前駆体（UV330nm付近、分子量150程度）が生成。鉄サビは局所の腐食・380nm寄与。</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>前駆体が生成する場。鉄サビ・付着物は450nmの主因でない（局所380nm）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="92" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>製品タンク
+(T-555)</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>窒素封入タンクで約6週間でAPHA&lt;5→25〜35。出口は規格内。残液は5/18(APHA30)以降は上昇せず。ドラム・SP（大気接触）は悪化なし。</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>GPCで分子量200〜800、GCの複数検体が457nmを捕捉＝ポリエナール。吸光度換算で数〜10ppb。酸素があると前駆体が有機酸へ酸化され縮合が進まない。</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>前駆体どうしが脱水縮合して共役が伸び450nm（黄）に。プール律速で、使い切るとAPHA30で頭打ち。共役系は微量で発色。</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>着色が成長する＝熟成の場。窒素で進行・大気で抑制。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>トータル＝1本の筋</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>触媒劣化で増えたアルデヒドが、アルドール縮合で高沸点の前駆体になってDEG留分へ移り、窒素タンクの長期保管で前駆体どうしが縮合・脱水して共役が伸び、約10ppb（推定）で450nm＝黄色に着色する。前駆体を使い切るとAPHA30程度で頭打ちになる。</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>注記：本筋は最有力仮説でRDベンチ未再現（タンク長期・低水分・塩基の同時再現が未達）。方向性は観測と整合。</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="4" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="A10:E10"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -699,101 +855,129 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>推定メカニズム（現時点の最有力仮説・ベンチでは未再現）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>段</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+          <t>発生事象と着色物質</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="64" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>① 起点：触媒選択性低下でアルデヒド増加</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>冬定修後のEO反応器触媒の選択性低下により、原料EO中のアルデヒド類（A-ALD・F-ALD）が増加した（原料EO中A-ALD/EO=0.78kg/t、過去実績の上位）。これがDEGまで持ち込まれる出発点。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="64" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>② 前駆体生成：アルドール縮合で共役の短い前駆体（MW150程度）</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>アルデヒドが後段で逐次的にアルドール縮合し、脱水（β-脱離）で共役二重結合が伸びた前駆体（UV330nm付近、分子量150程度）になる。縮合により高沸点化するため、軽質では届かないDEG留分まで移行する。アルドール縮合は塩基触媒で進み、酸素を必要としない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="64" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>③ 熟成：タンクで前駆体が反応し450nmへ（プール律速）</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>前駆体が製品タンクの常温・長期・窒素保管で、互いにアルドール型の縮合と脱水を繰り返して共役が伸び（分子量280〜300、上限側はオリゴマー化）、十分に伸びると450nm＝黄色の着色に至る。新規アルデヒドの付加ではなく上流で出来た前駆体プールの反応で、前駆体を使い切るとAPHA30程度で頭打ちになる（T-555残液が5/18以降上昇しないことと整合）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="64" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>④ 酸素の効き：大気接触では縮合が進みにくい</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>酸素があると、アルデヒド・前駆体が酸化されて有機酸になり、縮合（伸長）が進みにくくなる（発色団自体も酸化的に分解される）。窒素封入のタンクでは進行し、大気接触のドラム・SPでは抑制される——保管環境による差はこれで説明できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="64" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>一筋</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>触媒劣化で増えたアルデヒドが、アルドール縮合で高沸点の前駆体になってDEG留分へ移り、窒素タンクの長期保管で前駆体どうしが縮合・脱水して共役が伸び、約10ppb（推定）で450nm＝黄色に着色する。前駆体を使い切るとAPHA30程度で頭打ちになる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>本メカニズムは現時点の最有力仮説で、RDベンチでは再現に至っていない（タンク長期保管・pH・前駆体濃度の同時再現が未達）。方向性（共役が伸びて黄色になる／酸素で抑制される）は観測と整合する。</t>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>発生事象（事実）</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>冬定修後の再稼働（3月）以降、製品DEGがタンク保管中に色相（APHA）を経時上昇。約1か月半で検査規格を超過（APHA&lt;5 → 25〜35）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="10" t="inlineStr"/>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>プラント出口（ストリーム品）は常に規格内（APHA&lt;5）。タンク（窒素封入）で保管中にのみ上昇する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="10" t="inlineStr"/>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>同じ製品でも、ドラム充填品・SP転送品（大気接触）では色相上昇しない。共配ライン残液（27日保管）も悪化なし。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="10" t="inlineStr"/>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>色相・外観以外の品質規格（純度・MEG/TEG・水分・金属・蒸留性状）は実測で正常品の範囲内。pHのみ通常より僅かに高め（+0.1〜0.2程度）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>着色物質・現象（事実）</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>UVスペクトルで300nm付近と450nm付近に吸収。色相（APHA）上昇に伴い450nmが増大（450nmの補色＝黄、観測色と一致）。APHA30以上で550〜650nmにも吸収。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="10" t="inlineStr"/>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>450nm吸光度とAPHAが相関。GPCで分子量200〜800の分布。GCの複数検体が457nmを捕捉。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="10" t="inlineStr"/>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>T-555残液は5/18時点（APHA30）以降、APHAが上昇していない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="10" t="inlineStr"/>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>アルデヒド類（A-ALD・F-ALD・アクロレイン）も検出されるが、アクロレイン濃度とAPHAは相関しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>着色物質（推定）</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>着色物質は共役ポリエン（CH=CHの連なり）を持つ化合物の混合物と推定。共役が伸びるほど吸収が長波長化し、十分に伸びると可視域450nm（黄）に達する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="10" t="inlineStr"/>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>GPCの200〜800という幅は単一物質でなくオリゴマー混合物を示す（数平均の分子量はおよそ280〜300、上限側はオリゴマー化やグリコール付加で大きくなる）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="10" t="inlineStr"/>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>存在量はUV吸光度からの換算で数ppb〜10ppb程度（ppbオーダー、絶対定量は未確立）。共役系の吸光係数が極めて大きいため、この微量で色がつく。</t>
         </is>
       </c>
     </row>
@@ -823,103 +1007,103 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>要因（位置づけ）</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>対応</t>
         </is>
       </c>
     </row>
     <row r="3" ht="44" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>アルデヒドが多かった（必要条件）</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>触媒選択性低下でA-ALD・F-ALDが増加（A-ALD/EO=0.78kg/t、過去実績の上位）。種となるアルデヒドの絶対量が多かった。</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>→ 触媒交換で除去</t>
         </is>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>水分が少ない条件だった（促進）</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>脱水・縮合は水があると進みにくい平衡反応。脱水塔ボトムが低水分で縮合が進みやすかった。</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>→ 水分管理で確認</t>
         </is>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>塩基条件（苛性ソーダ）が後押し（促進）</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>NaOHの塩基がアルドール縮合を促進する側に働いた（NaOH→リン酸Na切替で330nm低下と整合）。</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>→ SU時はNaOH非投入</t>
         </is>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>DEG留分には樹脂（IER）が無い（DEG特有・除去機構の欠如）</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>MEG・TEGはイオン交換樹脂で前駆体を除去して製品を安定化できるが、DEG留分には樹脂が無く前駆体がそのまま製品に持ち込まれる。</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>→ 出口でDEGラインIERを検討</t>
         </is>
       </c>
     </row>
     <row r="7" ht="56" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>水分の注記</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>水分の解釈には注意が要る。2025年10月頃からMEG塔リボイラーの穴で水が混入し、脱水塔ボトム水分が高めに見えていた（50ppm台）。穴を修理した後は10ppm台へ低下し、複数点で再確認している。水分の時系列は『穴の前／穴のある期間／修理後』の3期に分けて評価する。</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr"/>
+      <c r="C7" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -935,171 +1119,173 @@
   <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="86" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>設備（鉄サビ・付着物）の関与の評価と開放・検査の整理</t>
+          <t>設備（鉄サビ・付着物）の評価と開放・検査</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>■ 鉄サビ・付着物の評価</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="B2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>C-1503トップに黒色付着物（XRFでほぼ鉄＝サビ）。水抽出からギ酸・グリコール酸を検出＝局所で有機酸が生じ腐食したものと整合。</t>
         </is>
       </c>
-      <c r="B3" s="11" t="n"/>
-    </row>
-    <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>この付着物をDEGに共存させてもλmax380nmが出るのみで、実機の450nmは再現しない。蒸留DEGの短時間保管でも450nmは出ない。</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n"/>
-    </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>T-555タンク内の異物も鉄サビだが、残液は5/18時点のAPHA30から上昇していない。</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n"/>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>以上より、鉄サビ・付着物は色相（450nm）を進める触媒ではなく、寄与は局所の腐食・380nmにとどまる（主因ではない）。保管試験・残液分析という実測で判断している。金属が無くてもアルデヒドとpHだけで着色は説明できる。付着物は予防保全として洗浄する。</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n"/>
+      <c r="B6" s="4" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>■ 開放・検査（機器ごと）</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n"/>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="B7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>機器</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>開放理由・結果</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>C-1503</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>ウォータージェットで付着物除去。付着物は450nmに寄与しないことを保管試験で確認。</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>C-1501トップ</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>開放しないと確認できないため清掃対応。</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>C-1501／C-1502／C-1504</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>インターナル・壁面とも過去と比べ問題なし。対応なし。</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>C-1501ボトムフィルター下流〜C-1502フィード配管</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>冬定修でSUS化済みのため錆込みなし。</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>リボイラー・コンデンサー等</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>塔本体が過去同様で問題なく、周辺は開放せず。</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>T-555／T-615（DEGタンク）</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>開放・洗浄。異物は鉄サビ（T-615右側サンプルは砂が過半＋鉄10〜12%）。</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>肉厚測定</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>定修前の運転中に各機器外側から測定。原肉に対し有意な減肉なし。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>開放は『推定メカニズムに基づき、縮合反応が起こり得る脱水塔以降に絞って当該機器を確認し、結果を仮説に沿って解釈する』順序で行う。機器を開けた結果から逆に範囲を決めるのではなく、技術→推定メカニズム→該当機器の確認→補足、の順とする。</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n"/>
+      <c r="B16" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A5:B5"/>
@@ -1119,9 +1305,9 @@
   <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="76" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="82" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,120 +1317,120 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>位置づけ</t>
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>状況</t>
         </is>
       </c>
     </row>
     <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>触媒交換（原因除去）</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>計画停止で触媒交換済。アルデヒド類の生成を抑える。</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t>実施済</t>
         </is>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>タンク・配管の洗浄</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>色相上昇を確認したタンク等を開放・洗浄し付着物を除去、保管設備を健全化。</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>実施済</t>
         </is>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>苛性ソーダ（NaOH）</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>スタートアップ時は投入しないベース。アルデヒドが多い局面ではアルドール縮合を促進し得るため、触媒交換後にアルデヒド低下を確認してから要否判断。</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>方針</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>MEG塔温度</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>下げない方針。温度を下げるとアルデヒドが分解されず前駆体として下流に回り、かえって色相側に出る懸念があるため。</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>方針</t>
         </is>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>リン酸ナトリウム（Na₃PO₄）</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>保管中反応の緩和策。pH低下で縮合を抑える／金属を不活性化する効きがある（効き方は要検証）。置換（払い出しを伴う入替）とセットで運用。</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>緩和・要検証</t>
         </is>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>出口（DEGラインのIER）</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>前段で抑えきれない場合の出口戦略として、DEGラインへの樹脂設置を検討（実DEGの通液テストを予定）。</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>検討中</t>
         </is>
@@ -1264,8 +1450,8 @@
   <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="86" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1276,136 +1462,136 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>■ 品質管理・早期判定</t>
         </is>
       </c>
-      <c r="B2" s="11" t="n"/>
+      <c r="B2" s="4" t="n"/>
     </row>
     <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>再稼働後の初期流動品は、APHAを含む社内規格全項目で規格内を確認。</t>
         </is>
       </c>
-      <c r="B3" s="11" t="n"/>
+      <c r="B3" s="4" t="n"/>
     </row>
     <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>初期流動品はタンク保管中の色相・UVスペクトルの経時変化が無いことを確認してから出荷。</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n"/>
+      <c r="B4" s="4" t="n"/>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>早期判定はUV450nmを主指標とする（悪化品は約0.004/日上昇、正常品は0.002で不動）。UV330nm（Na非含有領域）を補助に用いる。</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n"/>
+      <c r="B5" s="4" t="n"/>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>色相の律速は後段の縮合（UV450nm）であり、アルデヒド量は先行指標としての相関が弱い（アクロレインとAPHAも相関しない）。このためトータルアルデヒド監視は採用しない（現行のDNPH法以上の情報は得られない見込み）。</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n"/>
+      <c r="B6" s="4" t="n"/>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>ストリーム／タンクの切り分けのため、製品ストリームを窒素雰囲気のボンベで採取し経時を確認する。</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n"/>
+      <c r="B7" s="4" t="n"/>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>出荷再開の判定基準（オンスペック判定／タンク経時の観察期間／UV450nmの日次傾きの閾値／初期流動品の解除ロット数）は、本対策会議で具体値を確定する（決め事）。</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n"/>
+      <c r="B8" s="4" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>■ 残論点（要確認）</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n"/>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="B9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>論点</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>確認の方向</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>メカニズムのベンチ再現</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>アルデヒド添加だけではDEGの450nmが再現できていない。タンク長期保管・低水分・塩基などの条件併存を含め、再現性の確認が必要。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>リン酸の効き方</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>pH低下で縮合を抑えるのか、金属不活性化なのか。C-1503充填部のリン到達（壁面のリン分析）で切り分け。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="38" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>水分の寄与度</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>縮合への水分の効きは感度2〜3割の見立て。リボイラー穴の影響を除いた水分時系列（3期）で再評価する。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>着色物質のN分</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>GPC/GC-MSでN分含有の示唆。過去のアミン由来とは分子量が異なるが、N種の関与有無は要確認。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>前駆体の定量</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>前駆体・着色物質はppbオーダーで定量が困難。早期判定はUV系に絞る。</t>
         </is>

--- a/outputs/製品DEG色相悪化_事実整理.xlsx
+++ b/outputs/製品DEG色相悪化_事実整理.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別マトリクス" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別グリッド" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="発生事象・着色物質" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="なぜ今回起きたか" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設備・開放" sheetId="4" state="visible" r:id="rId4"/>
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,6 +46,24 @@
       <b val="1"/>
       <color rgb="00003F7E"/>
       <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <color rgb="00003F7E"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <color rgb="00C07A00"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <color rgb="00005BAB"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="游ゴシック"/>
@@ -76,12 +94,17 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBEFF2"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -95,12 +118,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FBF1DC"/>
+        <fgColor rgb="00E9F0F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E9F0F7"/>
+        <fgColor rgb="00F1F1F1"/>
       </patternFill>
     </fill>
     <fill>
@@ -115,7 +138,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EBEFF2"/>
+        <fgColor rgb="00FBF1DC"/>
       </patternFill>
     </fill>
   </fills>
@@ -189,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -205,52 +228,58 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -618,232 +647,388 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>製品DEG色相悪化　工程別の事実整理　→　1本の筋（仮説）</t>
+          <t>製品DEG色相悪化　工程別グリッド（横＝工程／縦＝項目）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>各工程で：①運転で見えた事実　②RDで検証した事実　③文献・この工程で起こる反応　→　④この工程の筋。全工程をトータルすると下段の1本の筋になる。</t>
+          <t>空欄＝確実な情報なし（無理に埋めない）。行の色＝根拠：緑＝事実（運転・解放・RD）／青＝文献・社外知見／灰＝一般原理／青灰＝小結論。上段の裏付け強度：◎事実複数で確定／○一部事実＋原理／△収支・原理のみで確度低。列を縦に見ると工程ごとの裏の厚さが分かる。</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
       <c r="C2" s="3" t="n"/>
       <c r="D2" s="3" t="n"/>
-      <c r="E2" s="4" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="4" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>項目</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>① 運転で見えた事実（運転・解放結果）</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>② RDで検証した事実（分析・ベンチ）</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>③ 文献・原理（この工程で起こる反応）</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>④ この工程の筋</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="92" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>EO反応器
-(R-1101)</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>原料EO中A-ALD/EO=0.78kg/t（過去実績の上位、通常0.11〜0.35）。F-ALDも増加。製品出口は規格内。</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>ラボでF/A-ALD添加→反応器出口相当でUV220/260が上昇。反応器で生じたUV成分はほぼそのまま後段へ持ち越す。</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
+          <t>EO反応系 (R-1101)</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>EG反応系 (R-1401)</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>EG濃縮系</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>EG脱水系 (C-1404)</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>MEG精製系 (C-1501/1502)</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>DEG精製系 (C-1503)</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>製品タンク (T-555)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>裏付け強度</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>① 運転で見えた事実</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>原料EO中A-ALD/EO=0.78kg/t（過去上位、通常0.11〜0.35）。F-ALDも増。</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>EG原料水中A-ALD 23ppm（過去最大相当）・F-ALD 4ppm。</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr"/>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>脱水塔ボトムは低水分（修理後10ppm台）。C-1404 BTM持込A-ALD 1〜2g/h。</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>C-1502トップでA-ALD一時異常高（3〜7ppm、過去1ppm以下）。脱水塔BTM・C-1501BTMは過去同水準。温度ダウンでHUV改善。</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>製品DEG出口は常に規格内（APHA&lt;5）。</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>窒素タンクで約6週APHA&lt;5→25〜35。残液は5/18(APHA30)以降上昇せず。ドラム・SP（大気）は悪化なし。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>② 解放・検査で見えた事実</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr"/>
+      <c r="C6" s="11" t="inlineStr"/>
+      <c r="D6" s="11" t="inlineStr"/>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>脱水塔の鉄錆除去（健全化）を実施。</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>C-1501/1502開放で異常な汚れ・活性金属なし。CS→SUS改造部も錆込みなし。</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>C-1503トップに黒色付着物（XRFでほぼ鉄＝サビ）。水抽出でギ酸70ppm・グリコール酸12ppm。</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>T-555/T-615開放。異物は鉄サビ（T-615右側は砂が過半＋鉄10〜12%）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>③ RDで検証した事実</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>ラボでF/A-ALD添加→反応器出口相当でUV220/260上昇。反応器生成UVは後段へほぼ持ち越し。</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>ラボEG反応器出口相当でALD添加→UV悪化（F-ALDとA-ALD共存で大）。</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr"/>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>ベンチで水分を増やすと縮合（UV）が2〜3割低下（感度の実測）。</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>C-1502トップA-ALD実測が物質収支の入量を上回る（生成項なしでは収支が閉じない）。</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>付着物＋DEG共存→λmax380nmのみで450nm再現せず。蒸留DEG短時間も450nm出ず。</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>GPC200〜800・GC457nm捕捉＝ポリエナール、数〜10ppb。酸素があると前駆体が有機酸へ酸化され縮合が進まない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>④ 文献・社外知見</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>シェル資料：F-ALD生成は反応器出口温度にアレニウス型。出口の錆除去・滞留短縮で低減。</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>シェル資料：DEG/TEGのエーテルがペルオキシ酸化で切断されMEG/DEG＋アルデヒドを生成。</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr"/>
+      <c r="E8" s="12" t="inlineStr"/>
+      <c r="F8" s="12" t="inlineStr"/>
+      <c r="G8" s="12" t="inlineStr"/>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>社外一般知見：アルデヒドのアルドール縮合で可視吸収のポリ不飽和体が生成し、pH制御で抑制（金属は必須でない）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>⑤ 一般原理（起こり得る反応）</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>触媒選択性低下でアルデヒド類が副生増。アルデヒドはアルドール縮合・着色の出発物質。</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>水和反応でEG生成。アルデヒドがグリコールと共存し始める。</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>収支上、A-ALDの大半はパージで系外（V-1402へ来るのは約35%）。軽質ALDは抜けるが一部は逃げ切って下流へ。</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>アルドール縮合は脱水を伴う平衡＝低水分で縮合側へ。縮合体は高沸点化して重質留分に残りやすい。</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>検出位置≠生成位置。重質縮合体が塔間循環で運ばれ、C-1502近傍でレトロアルドール的にALDへ戻って検出され得る。</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>塩基・高温下でアルドール縮合が進み、共役の短い前駆体（UV330nm付近・MW150程度）が生成。</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>前駆体どうしが脱水縮合して共役が伸び450nm（黄）。プール律速で使い切るとAPHA30で頭打ち。共役系は微量で発色。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>⑥ この工程で言えること</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>種となるアルデヒドが増えた＝着色の起点。</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="92" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>脱水塔まわり
-(C-1404)</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>脱水塔ボトムは低水分（修理後10ppm台）。※MEG塔リボイラーの穴で従来は50ppm台と誤認、修理後に低下。</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>水分があると縮合は進みにくい（脱水反応）。水分の効きは感度2〜3割の見立て。</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>アルドール縮合は脱水を伴う平衡。低水分ほど縮合（脱水）側へ寄る。</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>低水分が縮合を後押しする条件。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="92" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>MEG塔／リサイクル塔
-(C-1501/C-1502)</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>C-1502トップでA-ALDが一時的に異常高（3〜7ppm、過去1ppm以下）。脱水塔BTM・C-1501BTMは過去同水準。開放で異常な汚れ・活性金属なし（CS→SUS改造部も錆込みなし）。</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>物質収支上はC-1502でALD生成に見えるが、重質側で生じた縮合体が軽質ゆえ蒸留で上に運ばれた塔間循環で説明（検出位置≠生成位置）。</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>重質化した縮合体は蒸留系を循環し、一部はレトロ的に分解してALDに見える。</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>MEG系は着色の場ではない（活性金属なし）。縮合体が系内を回りDEG留分へ向かう通過点。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="92" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>DEG塔
-(C-1503)</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>C-1503トップに黒色付着物（XRFでほぼ鉄＝サビ）。水抽出でギ酸70ppm・グリコール酸12ppmを検出。</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>付着物をDEGに共存させてもλmax380nmのみで450nmは再現せず。蒸留DEGの短時間保管でも450nmは出ない。</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>塩基・高温下でアルドール縮合が進み、共役の短い前駆体（UV330nm付近、分子量150程度）が生成。鉄サビは局所の腐食・380nm寄与。</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>アルデヒドがEG生成系に持ち込まれ、UV成分の素地になる。</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>収支上は大半パージ・一部下流と推定（解放・RDの裏付けなし＝確度低）。</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>低水分が縮合を後押し。重質化し得る形（原理上）で下流へ運ばれる。</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>活性金属なし＝着色の生成場でない。C-1502の見かけ生成は循環由来の通過点（循環解釈は収支依存で要追検証）。</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>前駆体が生成する場。鉄サビ・付着物は450nmの主因でない（局所380nm）。</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="92" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>製品タンク
-(T-555)</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>窒素封入タンクで約6週間でAPHA&lt;5→25〜35。出口は規格内。残液は5/18(APHA30)以降は上昇せず。ドラム・SP（大気接触）は悪化なし。</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>GPCで分子量200〜800、GCの複数検体が457nmを捕捉＝ポリエナール。吸光度換算で数〜10ppb。酸素があると前駆体が有機酸へ酸化され縮合が進まない。</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>前駆体どうしが脱水縮合して共役が伸び450nm（黄）に。プール律速で、使い切るとAPHA30で頭打ち。共役系は微量で発色。</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>着色が成長する＝熟成の場。窒素で進行・大気で抑制。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>トータル＝1本の筋</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>触媒劣化で増えたアルデヒドが、アルドール縮合で高沸点の前駆体になってDEG留分へ移り、窒素タンクの長期保管で前駆体どうしが縮合・脱水して共役が伸び、約10ppb（推定）で450nm＝黄色に着色する。前駆体を使い切るとAPHA30程度で頭打ちになる。</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="4" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>注記：本筋は最有力仮説でRDベンチ未再現（タンク長期・低水分・塩基の同時再現が未達）。方向性は観測と整合。</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="4" t="n"/>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>着色が成長＝熟成の場。窒素で進行・大気で抑制。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>全工程をトータル＝1本の筋（仮説）</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>触媒劣化で増えたアルデヒドが、低水分・塩基条件で高沸点の前駆体（アルドール縮合体）になり、樹脂のないDEG留分を通って製品タンクへ。窒素タンクの長期保管で前駆体どうしが脱水縮合して共役が伸び、数〜10ppbで450nm＝黄色に着色する。前駆体を使い切るとAPHA30で頭打ち。</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>注記：本筋は最有力仮説でRDベンチ未再現（タンク長期・低水分・塩基の同時再現が未達）。文献・原理だけで事実の裏付けが薄い工程（空欄が多い列）は不確実性が大きい。</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="A10:E10"/>
+  <mergeCells count="4">
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A14:H14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -870,112 +1055,112 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
     <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>発生事象（事実）</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>冬定修後の再稼働（3月）以降、製品DEGがタンク保管中に色相（APHA）を経時上昇。約1か月半で検査規格を超過（APHA&lt;5 → 25〜35）。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="10" t="inlineStr"/>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr"/>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>プラント出口（ストリーム品）は常に規格内（APHA&lt;5）。タンク（窒素封入）で保管中にのみ上昇する。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="10" t="inlineStr"/>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr"/>
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>同じ製品でも、ドラム充填品・SP転送品（大気接触）では色相上昇しない。共配ライン残液（27日保管）も悪化なし。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="10" t="inlineStr"/>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr"/>
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>色相・外観以外の品質規格（純度・MEG/TEG・水分・金属・蒸留性状）は実測で正常品の範囲内。pHのみ通常より僅かに高め（+0.1〜0.2程度）。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>着色物質・現象（事実）</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>UVスペクトルで300nm付近と450nm付近に吸収。色相（APHA）上昇に伴い450nmが増大（450nmの補色＝黄、観測色と一致）。APHA30以上で550〜650nmにも吸収。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="10" t="inlineStr"/>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr"/>
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>450nm吸光度とAPHAが相関。GPCで分子量200〜800の分布。GCの複数検体が457nmを捕捉。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="10" t="inlineStr"/>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr"/>
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>T-555残液は5/18時点（APHA30）以降、APHAが上昇していない。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="10" t="inlineStr"/>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr"/>
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>アルデヒド類（A-ALD・F-ALD・アクロレイン）も検出されるが、アクロレイン濃度とAPHAは相関しない。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>着色物質（推定）</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>着色物質は共役ポリエン（CH=CHの連なり）を持つ化合物の混合物と推定。共役が伸びるほど吸収が長波長化し、十分に伸びると可視域450nm（黄）に達する。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="10" t="inlineStr"/>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr"/>
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>GPCの200〜800という幅は単一物質でなくオリゴマー混合物を示す（数平均の分子量はおよそ280〜300、上限側はオリゴマー化やグリコール付加で大きくなる）。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="10" t="inlineStr"/>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr"/>
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>存在量はUV吸光度からの換算で数ppb〜10ppb程度（ppbオーダー、絶対定量は未確立）。共役系の吸光係数が極めて大きいため、この微量で色がつく。</t>
         </is>
@@ -1008,102 +1193,102 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>要因（位置づけ）</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>対応</t>
         </is>
       </c>
     </row>
     <row r="3" ht="44" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>アルデヒドが多かった（必要条件）</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>触媒選択性低下でA-ALD・F-ALDが増加（A-ALD/EO=0.78kg/t、過去実績の上位）。種となるアルデヒドの絶対量が多かった。</t>
         </is>
       </c>
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>→ 触媒交換で除去</t>
         </is>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>水分が少ない条件だった（促進）</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>脱水・縮合は水があると進みにくい平衡反応。脱水塔ボトムが低水分で縮合が進みやすかった。</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>→ 水分管理で確認</t>
         </is>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>塩基条件（苛性ソーダ）が後押し（促進）</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>NaOHの塩基がアルドール縮合を促進する側に働いた（NaOH→リン酸Na切替で330nm低下と整合）。</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>→ SU時はNaOH非投入</t>
         </is>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>DEG留分には樹脂（IER）が無い（DEG特有・除去機構の欠如）</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>MEG・TEGはイオン交換樹脂で前駆体を除去して製品を安定化できるが、DEG留分には樹脂が無く前駆体がそのまま製品に持ち込まれる。</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>→ 出口でDEGラインIERを検討</t>
         </is>
       </c>
     </row>
     <row r="7" ht="56" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>水分の注記</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>水分の解釈には注意が要る。2025年10月頃からMEG塔リボイラーの穴で水が混入し、脱水塔ボトム水分が高めに見えていた（50ppm台）。穴を修理した後は10ppm台へ低下し、複数点で再確認している。水分の時系列は『穴の前／穴のある期間／修理後』の3期に分けて評価する。</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr"/>
+      <c r="C7" s="22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1131,7 +1316,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>■ 鉄サビ・付着物の評価</t>
         </is>
@@ -1139,7 +1324,7 @@
       <c r="B2" s="4" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>C-1503トップに黒色付着物（XRFでほぼ鉄＝サビ）。水抽出からギ酸・グリコール酸を検出＝局所で有機酸が生じ腐食したものと整合。</t>
         </is>
@@ -1147,7 +1332,7 @@
       <c r="B3" s="4" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>この付着物をDEGに共存させてもλmax380nmが出るのみで、実機の450nmは再現しない。蒸留DEGの短時間保管でも450nmは出ない。</t>
         </is>
@@ -1155,7 +1340,7 @@
       <c r="B4" s="4" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>T-555タンク内の異物も鉄サビだが、残液は5/18時点のAPHA30から上昇していない。</t>
         </is>
@@ -1163,7 +1348,7 @@
       <c r="B5" s="4" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>以上より、鉄サビ・付着物は色相（450nm）を進める触媒ではなく、寄与は局所の腐食・380nmにとどまる（主因ではない）。保管試験・残液分析という実測で判断している。金属が無くてもアルデヒドとpHだけで着色は説明できる。付着物は予防保全として洗浄する。</t>
         </is>
@@ -1171,7 +1356,7 @@
       <c r="B6" s="4" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>■ 開放・検査（機器ごと）</t>
         </is>
@@ -1179,96 +1364,96 @@
       <c r="B7" s="4" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>機器</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>開放理由・結果</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>C-1503</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>ウォータージェットで付着物除去。付着物は450nmに寄与しないことを保管試験で確認。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>C-1501トップ</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>開放しないと確認できないため清掃対応。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>C-1501／C-1502／C-1504</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>インターナル・壁面とも過去と比べ問題なし。対応なし。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>C-1501ボトムフィルター下流〜C-1502フィード配管</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>冬定修でSUS化済みのため錆込みなし。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>リボイラー・コンデンサー等</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>塔本体が過去同様で問題なく、周辺は開放せず。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>T-555／T-615（DEGタンク）</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>開放・洗浄。異物は鉄サビ（T-615右側サンプルは砂が過半＋鉄10〜12%）。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>肉厚測定</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>定修前の運転中に各機器外側から測定。原肉に対し有意な減肉なし。</t>
         </is>
@@ -1318,119 +1503,119 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>状況</t>
         </is>
       </c>
     </row>
     <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>触媒交換（原因除去）</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>計画停止で触媒交換済。アルデヒド類の生成を抑える。</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>実施済</t>
         </is>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>タンク・配管の洗浄</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>色相上昇を確認したタンク等を開放・洗浄し付着物を除去、保管設備を健全化。</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>実施済</t>
         </is>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>苛性ソーダ（NaOH）</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>スタートアップ時は投入しないベース。アルデヒドが多い局面ではアルドール縮合を促進し得るため、触媒交換後にアルデヒド低下を確認してから要否判断。</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t>方針</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>MEG塔温度</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>下げない方針。温度を下げるとアルデヒドが分解されず前駆体として下流に回り、かえって色相側に出る懸念があるため。</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>方針</t>
         </is>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>リン酸ナトリウム（Na₃PO₄）</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>保管中反応の緩和策。pH低下で縮合を抑える／金属を不活性化する効きがある（効き方は要検証）。置換（払い出しを伴う入替）とセットで運用。</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>緩和・要検証</t>
         </is>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>出口（DEGラインのIER）</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>前段で抑えきれない場合の出口戦略として、DEGラインへの樹脂設置を検討（実DEGの通液テストを予定）。</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>検討中</t>
         </is>
@@ -1462,7 +1647,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>■ 品質管理・早期判定</t>
         </is>
@@ -1470,7 +1655,7 @@
       <c r="B2" s="4" t="n"/>
     </row>
     <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>再稼働後の初期流動品は、APHAを含む社内規格全項目で規格内を確認。</t>
         </is>
@@ -1478,7 +1663,7 @@
       <c r="B3" s="4" t="n"/>
     </row>
     <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>初期流動品はタンク保管中の色相・UVスペクトルの経時変化が無いことを確認してから出荷。</t>
         </is>
@@ -1486,7 +1671,7 @@
       <c r="B4" s="4" t="n"/>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>早期判定はUV450nmを主指標とする（悪化品は約0.004/日上昇、正常品は0.002で不動）。UV330nm（Na非含有領域）を補助に用いる。</t>
         </is>
@@ -1494,7 +1679,7 @@
       <c r="B5" s="4" t="n"/>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>色相の律速は後段の縮合（UV450nm）であり、アルデヒド量は先行指標としての相関が弱い（アクロレインとAPHAも相関しない）。このためトータルアルデヒド監視は採用しない（現行のDNPH法以上の情報は得られない見込み）。</t>
         </is>
@@ -1502,7 +1687,7 @@
       <c r="B6" s="4" t="n"/>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>ストリーム／タンクの切り分けのため、製品ストリームを窒素雰囲気のボンベで採取し経時を確認する。</t>
         </is>
@@ -1510,7 +1695,7 @@
       <c r="B7" s="4" t="n"/>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>出荷再開の判定基準（オンスペック判定／タンク経時の観察期間／UV450nmの日次傾きの閾値／初期流動品の解除ロット数）は、本対策会議で具体値を確定する（決め事）。</t>
         </is>
@@ -1518,7 +1703,7 @@
       <c r="B8" s="4" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>■ 残論点（要確認）</t>
         </is>
@@ -1526,72 +1711,72 @@
       <c r="B9" s="4" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>論点</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>確認の方向</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>メカニズムのベンチ再現</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>アルデヒド添加だけではDEGの450nmが再現できていない。タンク長期保管・低水分・塩基などの条件併存を含め、再現性の確認が必要。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>リン酸の効き方</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>pH低下で縮合を抑えるのか、金属不活性化なのか。C-1503充填部のリン到達（壁面のリン分析）で切り分け。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="38" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>水分の寄与度</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>縮合への水分の効きは感度2〜3割の見立て。リボイラー穴の影響を除いた水分時系列（3期）で再評価する。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>着色物質のN分</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>GPC/GC-MSでN分含有の示唆。過去のアミン由来とは分子量が異なるが、N種の関与有無は要確認。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>前駆体の定量</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>前駆体・着色物質はppbオーダーで定量が困難。早期判定はUV系に絞る。</t>
         </is>

--- a/outputs/製品DEG色相悪化_事実整理.xlsx
+++ b/outputs/製品DEG色相悪化_事実整理.xlsx
@@ -998,7 +998,7 @@
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>触媒劣化で増えたアルデヒドが、低水分・塩基条件で高沸点の前駆体（アルドール縮合体）になり、樹脂のないDEG留分を通って製品タンクへ。窒素タンクの長期保管で前駆体どうしが脱水縮合して共役が伸び、数〜10ppbで450nm＝黄色に着色する。前駆体を使い切るとAPHA30で頭打ち。</t>
+          <t>触媒劣化で増えたアルデヒドが、低水分・塩基条件で高沸点の前駆体（アルドール縮合体）になり、樹脂のないDEG留分を通って製品タンクへ。窒素タンクの長期保管で前駆体どうしが脱水縮合して共役が伸び、ppbオーダーで450nm＝黄色に着色する。前駆体を使い切るとAPHA30で頭打ち。</t>
         </is>
       </c>
       <c r="B13" s="3" t="n"/>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>UVスペクトルで300nm付近と450nm付近に吸収。色相（APHA）上昇に伴い450nmが増大（450nmの補色＝黄、観測色と一致）。APHA30以上で550〜650nmにも吸収。</t>
+          <t>UVスペクトルで300nm付近と450nm付近に吸収。色相（APHA）上昇に伴い450nmが増大（450nmの補色＝黄、観測色と一致）。</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       <c r="A12" s="18" t="inlineStr"/>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>GPCの200〜800という幅は単一物質でなくオリゴマー混合物を示す（数平均の分子量はおよそ280〜300、上限側はオリゴマー化やグリコール付加で大きくなる）。</t>
+          <t>GPCの200〜800という幅は単一物質でなくオリゴマー混合物を示す（分子量は数百のオーダー、上限側はオリゴマー化で大きくなる）。</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       <c r="A13" s="18" t="inlineStr"/>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>存在量はUV吸光度からの換算で数ppb〜10ppb程度（ppbオーダー、絶対定量は未確立）。共役系の吸光係数が極めて大きいため、この微量で色がつく。</t>
+          <t>存在量は絶対定量が未確立だがppbオーダーの微量（UV吸光度からの換算）。共役系の吸光係数が大きく、微量で色がつく。</t>
         </is>
       </c>
     </row>

--- a/outputs/製品DEG色相悪化_事実整理.xlsx
+++ b/outputs/製品DEG色相悪化_事実整理.xlsx
@@ -1632,7 +1632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1705,88 +1705,202 @@
     <row r="9">
       <c r="A9" s="23" t="inlineStr">
         <is>
+          <t>■ 出荷判定の運用（歯止め）</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>メカニズム（仮説）の真偽に依らず、この出口実測の歯止めで出荷可否を判定する。「本会議で確定」とした具体値（日数・閾値・承認者・回収範囲）を本対策会議で固める。</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>運用（「本会議で確定」＝具体値は対策会議で固める）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>監視項目</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>APHA（全項目規格）＋UV450nm（早期判定の主指標）＋UV330nm（補助）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>監視期間</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>タンク保管中の経時を確認（必要日数は本会議で確定。UV450は実績上1日後から傾きで判別可）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>合格基準</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>全項目が規格内、かつUV450nmの日次の傾きが基準内（傾き上限・累積ΔAPHAの具体値は本会議で確定）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>出荷可否の承認</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>確認結果に基づき出荷可否を判断（承認の担当・手順は本会議で確定）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>出荷停止トリガー</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>初期流動品が規格内でも、その後UV450の傾きが基準を超えたら出荷停止。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>在庫回収の範囲</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>停止時の対象ロット範囲をあらかじめ規定（本会議で確定）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>早期判定の保険</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>UV450単独に依らず、全項目規格内を必須とし保守的マージンを併用（偽陰性対策）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
           <t>■ 残論点（要確認）</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="B19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>論点</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>確認の方向</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="38" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
+    <row r="21" ht="38" customHeight="1">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>メカニズムのベンチ再現</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>アルデヒド添加だけではDEGの450nmが再現できていない。タンク長期保管・低水分・塩基などの条件併存を含め、再現性の確認が必要。</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="38" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+    <row r="22" ht="38" customHeight="1">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>リン酸の効き方</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>pH低下で縮合を抑えるのか、金属不活性化なのか。C-1503充填部のリン到達（壁面のリン分析）で切り分け。</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="38" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
+    <row r="23" ht="38" customHeight="1">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>水分の寄与度</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>縮合への水分の効きは感度2〜3割の見立て。リボイラー穴の影響を除いた水分時系列（3期）で再評価する。</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+    <row r="24" ht="38" customHeight="1">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>着色物質のN分</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>GPC/GC-MSでN分含有の示唆。過去のアミン由来とは分子量が異なるが、N種の関与有無は要確認。</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
+    <row r="25" ht="38" customHeight="1">
+      <c r="A25" s="18" t="inlineStr">
         <is>
           <t>前駆体の定量</t>
         </is>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>前駆体・着色物質はppbオーダーで定量が困難。早期判定はUV系に絞る。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A10:B10"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A8:B8"/>

--- a/outputs/製品DEG色相悪化_事実整理.xlsx
+++ b/outputs/製品DEG色相悪化_事実整理.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -83,6 +83,11 @@
     </font>
     <font>
       <name val="游ゴシック"/>
+      <color rgb="00555555"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
       <b val="1"/>
       <color rgb="00005BAB"/>
       <sz val="10.5"/>
@@ -94,7 +99,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -118,11 +123,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E9F0F7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00F1F1F1"/>
       </patternFill>
     </fill>
@@ -134,11 +134,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00005BAB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FBF1DC"/>
       </patternFill>
     </fill>
   </fills>
@@ -212,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -249,13 +244,10 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -270,13 +262,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -647,7 +636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -773,23 +762,27 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>原料EO中A-ALD/EO=0.78kg/t（過去上位、通常0.11〜0.35）。F-ALDも増。</t>
+          <t>触媒選択性の低下で、アルデヒド類（A-ALD・F-ALD）の副生が増えた。</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>EG原料水中A-ALD 23ppm（過去最大相当）・F-ALD 4ppm。</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr"/>
+          <t>原料EO中のA-ALD/EO＝0.78kg/t（過去実績の上位、通常0.11〜0.35）。F-ALDも増加。</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>EG濃縮系出口（C-1403ボトム）のアルデヒド濃度は過去並み。</t>
+        </is>
+      </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>脱水塔ボトムは低水分（修理後10ppm台）。C-1404 BTM持込A-ALD 1〜2g/h。</t>
+          <t>EG脱水塔ボトム（C-1404）のアルデヒド濃度は過去並み。</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>C-1502トップでA-ALD一時異常高（3〜7ppm、過去1ppm以下）。脱水塔BTM・C-1501BTMは過去同水準。温度ダウンでHUV改善。</t>
+          <t>MEG精製塔C-1502トップでA-ALDが一時的に異常高（3〜7ppm、過去1ppm以下）。物質収支の入量より多い。C-1501塔底温度を下げるとA-ALDが低下。</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
@@ -799,14 +792,14 @@
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>窒素タンクで約6週APHA&lt;5→25〜35。残液は5/18(APHA30)以降上昇せず。ドラム・SP（大気）は悪化なし。</t>
+          <t>窒素封入タンクで約6週間にAPHA&lt;5→25〜35へ上昇。残液は5/18（APHA30）以降は上昇せず。大気接触のドラム・SPでは進まない。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="70" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>② 解放・検査で見えた事実</t>
+          <t>② 開放・検査で見えた事実</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr"/>
@@ -814,22 +807,22 @@
       <c r="D6" s="11" t="inlineStr"/>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>脱水塔の鉄錆除去（健全化）を実施。</t>
+          <t>EG脱水塔の鉄錆を除去（健全化）。</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>C-1501/1502開放で異常な汚れ・活性金属なし。CS→SUS改造部も錆込みなし。</t>
+          <t>MEG精製塔C-1501／C-1502を開放、異常な汚れ・活性金属なし。C-1501塔底〜C-1502配管のSUS化部も錆込みなし。</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>C-1503トップに黒色付着物（XRFでほぼ鉄＝サビ）。水抽出でギ酸70ppm・グリコール酸12ppm。</t>
+          <t>DEG精製塔C-1503トップに黒色付着物（XRFでほぼ鉄＝サビ）。水抽出でギ酸70ppm・グリコール酸12ppm。</t>
         </is>
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>T-555/T-615開放。異物は鉄サビ（T-615右側は砂が過半＋鉄10〜12%）。</t>
+          <t>製品タンクT-555／T-615を開放。異物は鉄サビ（T-615の一部は砂が過半＋鉄10〜12%）。</t>
         </is>
       </c>
     </row>
@@ -839,152 +832,128 @@
           <t>③ RDで検証した事実</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>ラボでF/A-ALD添加→反応器出口相当でUV220/260上昇。反応器生成UVは後段へほぼ持ち越し。</t>
-        </is>
-      </c>
+      <c r="B7" s="11" t="inlineStr"/>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>ラボEG反応器出口相当でALD添加→UV悪化（F-ALDとA-ALD共存で大）。</t>
+          <t>ラボでEG反応器出口を模擬し、F-ALD・A-ALDを添加するとUVが悪化（両者の共存でより大きい）。</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr"/>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>ベンチで水分を増やすと縮合（UV）が2〜3割低下（感度の実測）。</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>C-1502トップA-ALD実測が物質収支の入量を上回る（生成項なしでは収支が閉じない）。</t>
-        </is>
-      </c>
+          <t>基礎研の見立てでは、水分が多いほど縮合は進みにくく、効きは感度として全体の2〜3割程度。</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr"/>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>付着物＋DEG共存→λmax380nmのみで450nm再現せず。蒸留DEG短時間も450nm出ず。</t>
+          <t>C-1503の付着物をDEGに加えて保管すると380nmの吸収は出るが、実機の450nmは出ない。蒸留DEGを短時間置いても450nmは出ない＝付着物は実機の着色（450nm）を作らない。</t>
         </is>
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>GPC200〜800・GC457nm捕捉＝ポリエナール、数〜10ppb。酸素があると前駆体が有機酸へ酸化され縮合が進まない。</t>
+          <t>着色物質をGPC・GCで分析＝分子量200〜800・457nm吸収のポリエナール（ppbオーダー）。酸素があると前駆体が有機酸へ酸化され、縮合が進まない。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="70" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>④ 文献・社外知見</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>シェル資料：F-ALD生成は反応器出口温度にアレニウス型。出口の錆除去・滞留短縮で低減。</t>
-        </is>
-      </c>
+          <t>④ 一般原理（起こり得る反応）</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr"/>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>シェル資料：DEG/TEGのエーテルがペルオキシ酸化で切断されMEG/DEG＋アルデヒドを生成。</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr"/>
-      <c r="E8" s="12" t="inlineStr"/>
-      <c r="F8" s="12" t="inlineStr"/>
-      <c r="G8" s="12" t="inlineStr"/>
+          <t>水和反応でEGを生成。ここでアルデヒドがグリコールと共存し始める。</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>アルデヒドの大半は蒸気側からパージで系外へ。軽いアルデヒドは抜けるが、一部は下流へ持ち込まれ得る。</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>アルドール縮合は水を出す平衡反応で、水が少ないほど縮合が進む。縮合した重い化合物は沸点が高く、重質側（DEG留分）に残りやすい。</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>検出位置＝生成位置とは限らない。重い縮合物が塔間の循環で運ばれ、C-1502付近でレトロアルドールによりアルデヒドに戻って検出され得る。</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>塩基性・高温下でアルドール縮合が進み、共役の短い前駆体（UV330nm付近・分子量150程度）ができる。</t>
+        </is>
+      </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>社外一般知見：アルデヒドのアルドール縮合で可視吸収のポリ不飽和体が生成し、pH制御で抑制（金属は必須でない）。</t>
+          <t>前駆体どうしがさらに脱水縮合して共役が伸び、450nm（黄）に達する。前駆体を使い切るとAPHA30程度で頭打ち。共役系は微量で発色する。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="70" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>⑤ 一般原理（起こり得る反応）</t>
+          <t>⑤ この工程で言えること</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>触媒選択性低下でアルデヒド類が副生増。アルデヒドはアルドール縮合・着色の出発物質。</t>
+          <t>種となるアルデヒドが増えた＝着色の起点。</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>水和反応でEG生成。アルデヒドがグリコールと共存し始める。</t>
+          <t>アルデヒドがEG生成系に持ち込まれ、UV成分の素地になる。</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>収支上、A-ALDの大半はパージで系外（V-1402へ来るのは約35%）。軽質ALDは抜けるが一部は逃げ切って下流へ。</t>
+          <t>大半はパージされ、一部が下流へ持ち込まれ得る。</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>アルドール縮合は脱水を伴う平衡＝低水分で縮合側へ。縮合体は高沸点化して重質留分に残りやすい。</t>
+          <t>アルデヒドが多い条件では、ここで縮合が進み、重い形で下流へ運ばれ得る。</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>検出位置≠生成位置。重質縮合体が塔間循環で運ばれ、C-1502近傍でレトロアルドール的にALDへ戻って検出され得る。</t>
+          <t>活性金属がなく、着色の生成場ではない。C-1502の見かけの生成は循環由来で通過点（要追検証）。</t>
         </is>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>塩基・高温下でアルドール縮合が進み、共役の短い前駆体（UV330nm付近・MW150程度）が生成。</t>
+          <t>前駆体が生成する場。鉄サビ・付着物は450nmの主因ではない（局所の380nm）。</t>
         </is>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
-          <t>前駆体どうしが脱水縮合して共役が伸び450nm（黄）。プール律速で使い切るとAPHA30で頭打ち。共役系は微量で発色。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>⑥ この工程で言えること</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>種となるアルデヒドが増えた＝着色の起点。</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>アルデヒドがEG生成系に持ち込まれ、UV成分の素地になる。</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>収支上は大半パージ・一部下流と推定（解放・RDの裏付けなし＝確度低）。</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>低水分が縮合を後押し。重質化し得る形（原理上）で下流へ運ばれる。</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="inlineStr">
-        <is>
-          <t>活性金属なし＝着色の生成場でない。C-1502の見かけ生成は循環由来の通過点（循環解釈は収支依存で要追検証）。</t>
-        </is>
-      </c>
-      <c r="G10" s="14" t="inlineStr">
-        <is>
-          <t>前駆体が生成する場。鉄サビ・付着物は450nmの主因でない（局所380nm）。</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>着色が成長＝熟成の場。窒素で進行・大気で抑制。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
+          <t>着色が成長する＝熟成の場。窒素で進み、大気で止まる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>全工程をトータル＝1本の筋（仮説）</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="52" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>全工程をトータル＝1本の筋（仮説）</t>
+          <t>触媒劣化で増えたアルデヒドが、脱水以降の塔（元々水が少ない）と塩基条件のもとで縮合して重い前駆体になり、樹脂のないDEG留分を通って製品タンクへ。窒素タンクの長期保管で前駆体どうしが脱水縮合して共役が伸び、ppbオーダーで450nm＝黄色に着色する。前駆体を使い切るとAPHA30で頭打ち。</t>
         </is>
       </c>
       <c r="B12" s="3" t="n"/>
@@ -995,10 +964,10 @@
       <c r="G12" s="3" t="n"/>
       <c r="H12" s="4" t="n"/>
     </row>
-    <row r="13" ht="52" customHeight="1">
+    <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>触媒劣化で増えたアルデヒドが、低水分・塩基条件で高沸点の前駆体（アルドール縮合体）になり、樹脂のないDEG留分を通って製品タンクへ。窒素タンクの長期保管で前駆体どうしが脱水縮合して共役が伸び、ppbオーダーで450nm＝黄色に着色する。前駆体を使い切るとAPHA30で頭打ち。</t>
+          <t>注記：本筋は最有力仮説でRDベンチ未再現（タンク長期・低水分・塩基の同時再現が未達）。文献・原理だけで事実の裏付けが薄い工程（空欄が多い列）は不確実性が大きい。</t>
         </is>
       </c>
       <c r="B13" s="3" t="n"/>
@@ -1009,26 +978,12 @@
       <c r="G13" s="3" t="n"/>
       <c r="H13" s="4" t="n"/>
     </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>注記：本筋は最有力仮説でRDベンチ未再現（タンク長期・低水分・塩基の同時再現が未達）。文献・原理だけで事実の裏付けが薄い工程（空欄が多い列）は不確実性が大きい。</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="4" t="n"/>
-    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A11:H11"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A14:H14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1067,100 +1022,100 @@
       </c>
     </row>
     <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>発生事象（事実）</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>冬定修後の再稼働（3月）以降、製品DEGがタンク保管中に色相（APHA）を経時上昇。約1か月半で検査規格を超過（APHA&lt;5 → 25〜35）。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="18" t="inlineStr"/>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr"/>
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>プラント出口（ストリーム品）は常に規格内（APHA&lt;5）。タンク（窒素封入）で保管中にのみ上昇する。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="18" t="inlineStr"/>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>同じ製品でも、ドラム充填品・SP転送品（大気接触）では色相上昇しない。共配ライン残液（27日保管）も悪化なし。</t>
+      <c r="A5" s="17" t="inlineStr"/>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>大気接触（ドラム充填・SP転送）では色相が進まず、悪化したものも大気に触れると進行が止まる。共配ライン残液も悪化していない。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="18" t="inlineStr"/>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr"/>
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>色相・外観以外の品質規格（純度・MEG/TEG・水分・金属・蒸留性状）は実測で正常品の範囲内。pHのみ通常より僅かに高め（+0.1〜0.2程度）。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>着色物質・現象（事実）</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>UVスペクトルで300nm付近と450nm付近に吸収。色相（APHA）上昇に伴い450nmが増大（450nmの補色＝黄、観測色と一致）。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="18" t="inlineStr"/>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr"/>
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>450nm吸光度とAPHAが相関。GPCで分子量200〜800の分布。GCの複数検体が457nmを捕捉。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="18" t="inlineStr"/>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr"/>
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>T-555残液は5/18時点（APHA30）以降、APHAが上昇していない。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="18" t="inlineStr"/>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr"/>
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>アルデヒド類（A-ALD・F-ALD・アクロレイン）も検出されるが、アクロレイン濃度とAPHAは相関しない。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>着色物質（推定）</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>着色物質は共役ポリエン（CH=CHの連なり）を持つ化合物の混合物と推定。共役が伸びるほど吸収が長波長化し、十分に伸びると可視域450nm（黄）に達する。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="18" t="inlineStr"/>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr"/>
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>GPCの200〜800という幅は単一物質でなくオリゴマー混合物を示す（分子量は数百のオーダー、上限側はオリゴマー化で大きくなる）。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="18" t="inlineStr"/>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr"/>
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>存在量は絶対定量が未確立だがppbオーダーの微量（UV吸光度からの換算）。共役系の吸光係数が大きく、微量で色がつく。</t>
         </is>
@@ -1177,7 +1132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1188,109 +1143,91 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>なぜ今回だけDEGまで到達し着色したか（条件の重なり）</t>
+          <t>なぜ今回だけDEGまで到達し着色したか</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>脱水以降の塔は元々水分が少なく、アルデヒドが多いと縮合が進みやすい。脱水のプロセスを変えたわけではなく、今回はアルデヒドが多かったことが引き金で、塩基条件とDEG特有の事情が重なった。</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>要因（位置づけ）</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>対応</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="44" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
-        <is>
-          <t>アルデヒドが多かった（必要条件）</t>
-        </is>
-      </c>
-      <c r="B3" s="19" t="inlineStr">
-        <is>
-          <t>触媒選択性低下でA-ALD・F-ALDが増加（A-ALD/EO=0.78kg/t、過去実績の上位）。種となるアルデヒドの絶対量が多かった。</t>
-        </is>
-      </c>
-      <c r="C3" s="20" t="inlineStr">
+    <row r="4" ht="46" customHeight="1">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>アルデヒドが過去最大級に多かった（引き金）</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>触媒選択性の低下でA-ALD・F-ALDが増加（原料EO中A-ALD/EO=0.78kg/t、過去実績の上位）。種となるアルデヒドの絶対量が多かった。</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>→ 触媒交換で除去</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="44" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t>水分が少ない条件だった（促進）</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>脱水・縮合は水があると進みにくい平衡反応。脱水塔ボトムが低水分で縮合が進みやすかった。</t>
-        </is>
-      </c>
-      <c r="C4" s="20" t="inlineStr">
-        <is>
-          <t>→ 水分管理で確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>塩基条件（苛性ソーダ）が後押し（促進）</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>NaOHの塩基がアルドール縮合を促進する側に働いた（NaOH→リン酸Na切替で330nm低下と整合）。</t>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>塩基条件（苛性ソーダ）が縮合を後押しした（促進）</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>NaOHの塩基がアルドール縮合を促進する側に働いた（NaOHからリン酸Naへ切替で330nmが低下した実績と整合）。</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>→ SU時はNaOH非投入</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>DEG留分には樹脂（IER）が無い（DEG特有・除去機構の欠如）</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>MEG・TEGはイオン交換樹脂で前駆体を除去して製品を安定化できるが、DEG留分には樹脂が無く前駆体がそのまま製品に持ち込まれる。</t>
+          <t>→ スタートアップ時はNaOH非投入</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>DEG留分には樹脂（IER）が無い（DEG特有の事情）</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>MEG・TEGはイオン交換樹脂で前駆体を除去して製品を安定化できるが、DEG留分には樹脂が無く、前駆体がそのまま製品に残る。</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>→ 出口でDEGラインIERを検討</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="56" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
-        <is>
-          <t>水分の注記</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>水分の解釈には注意が要る。2025年10月頃からMEG塔リボイラーの穴で水が混入し、脱水塔ボトム水分が高めに見えていた（50ppm台）。穴を修理した後は10ppm台へ低下し、複数点で再確認している。水分の時系列は『穴の前／穴のある期間／修理後』の3期に分けて評価する。</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr"/>
+          <t>→ 出口でDEGラインのIERを検討</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1316,7 +1253,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>■ 鉄サビ・付着物の評価</t>
         </is>
@@ -1324,7 +1261,7 @@
       <c r="B2" s="4" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>C-1503トップに黒色付着物（XRFでほぼ鉄＝サビ）。水抽出からギ酸・グリコール酸を検出＝局所で有機酸が生じ腐食したものと整合。</t>
         </is>
@@ -1332,7 +1269,7 @@
       <c r="B3" s="4" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>この付着物をDEGに共存させてもλmax380nmが出るのみで、実機の450nmは再現しない。蒸留DEGの短時間保管でも450nmは出ない。</t>
         </is>
@@ -1340,7 +1277,7 @@
       <c r="B4" s="4" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>T-555タンク内の異物も鉄サビだが、残液は5/18時点のAPHA30から上昇していない。</t>
         </is>
@@ -1348,15 +1285,15 @@
       <c r="B5" s="4" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>以上より、鉄サビ・付着物は色相（450nm）を進める触媒ではなく、寄与は局所の腐食・380nmにとどまる（主因ではない）。保管試験・残液分析という実測で判断している。金属が無くてもアルデヒドとpHだけで着色は説明できる。付着物は予防保全として洗浄する。</t>
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>以上より、鉄サビ・付着物は色相（450nm）を進める触媒ではなく、寄与は局所の腐食・380nmにとどまる（主因ではない）。保管試験・残液分析という実測で判断している。付着物は洗浄して除去する。</t>
         </is>
       </c>
       <c r="B6" s="4" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>■ 開放・検査（機器ごと）</t>
         </is>
@@ -1376,84 +1313,84 @@
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>C-1503</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>ウォータージェットで付着物除去。付着物は450nmに寄与しないことを保管試験で確認。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>C-1501トップ</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>開放しないと確認できないため清掃対応。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>C-1501／C-1502／C-1504</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>インターナル・壁面とも過去と比べ問題なし。対応なし。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>C-1501ボトムフィルター下流〜C-1502フィード配管</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>冬定修でSUS化済みのため錆込みなし。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>リボイラー・コンデンサー等</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>塔本体が過去同様で問題なく、周辺は開放せず。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>T-555／T-615（DEGタンク）</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>開放・洗浄。異物は鉄サビ（T-615右側サンプルは砂が過半＋鉄10〜12%）。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>肉厚測定</t>
         </is>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>定修前の運転中に各機器外側から測定。原肉に対し有意な減肉なし。</t>
         </is>
@@ -1462,7 +1399,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>開放は『推定メカニズムに基づき、縮合反応が起こり得る脱水塔以降に絞って当該機器を確認し、結果を仮説に沿って解釈する』順序で行う。機器を開けた結果から逆に範囲を決めるのではなく、技術→推定メカニズム→該当機器の確認→補足、の順とする。</t>
+          <t>今定修で開放・検査した箇所の結果を整理した。いずれも色相（450nm）の主因となる異常はなく、推定メカニズム（縮合は脱水塔以降で起こる）とも整合する。結果から範囲を決めたのではなく、確認結果を仮説に沿って位置づけている。</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -1520,102 +1457,102 @@
       </c>
     </row>
     <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>触媒交換（原因除去）</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>計画停止で触媒交換済。アルデヒド類の生成を抑える。</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t>実施済</t>
         </is>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>タンク・配管の洗浄</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>色相上昇を確認したタンク等を開放・洗浄し付着物を除去、保管設備を健全化。</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>実施済</t>
         </is>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>苛性ソーダ（NaOH）</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>スタートアップ時は投入しないベース。アルデヒドが多い局面ではアルドール縮合を促進し得るため、触媒交換後にアルデヒド低下を確認してから要否判断。</t>
         </is>
       </c>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>方針</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>MEG塔温度</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>下げない方針。温度を下げるとアルデヒドが分解されず前駆体として下流に回り、かえって色相側に出る懸念があるため。</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>方針</t>
         </is>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>リン酸ナトリウム（Na₃PO₄）</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>保管中反応の緩和策。pH低下で縮合を抑える／金属を不活性化する効きがある（効き方は要検証）。置換（払い出しを伴う入替）とセットで運用。</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>緩和・要検証</t>
         </is>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>出口（DEGラインのIER）</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>前段で抑えきれない場合の出口戦略として、DEGラインへの樹脂設置を検討（実DEGの通液テストを予定）。</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>検討中</t>
         </is>
@@ -1647,7 +1584,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>■ 品質管理・早期判定</t>
         </is>
@@ -1655,7 +1592,7 @@
       <c r="B2" s="4" t="n"/>
     </row>
     <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>再稼働後の初期流動品は、APHAを含む社内規格全項目で規格内を確認。</t>
         </is>
@@ -1663,7 +1600,7 @@
       <c r="B3" s="4" t="n"/>
     </row>
     <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>初期流動品はタンク保管中の色相・UVスペクトルの経時変化が無いことを確認してから出荷。</t>
         </is>
@@ -1671,7 +1608,7 @@
       <c r="B4" s="4" t="n"/>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>早期判定はUV450nmを主指標とする（悪化品は約0.004/日上昇、正常品は0.002で不動）。UV330nm（Na非含有領域）を補助に用いる。</t>
         </is>
@@ -1679,7 +1616,7 @@
       <c r="B5" s="4" t="n"/>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>色相の律速は後段の縮合（UV450nm）であり、アルデヒド量は先行指標としての相関が弱い（アクロレインとAPHAも相関しない）。このためトータルアルデヒド監視は採用しない（現行のDNPH法以上の情報は得られない見込み）。</t>
         </is>
@@ -1687,7 +1624,7 @@
       <c r="B6" s="4" t="n"/>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>ストリーム／タンクの切り分けのため、製品ストリームを窒素雰囲気のボンベで採取し経時を確認する。</t>
         </is>
@@ -1695,7 +1632,7 @@
       <c r="B7" s="4" t="n"/>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>出荷再開の判定基準（オンスペック判定／タンク経時の観察期間／UV450nmの日次傾きの閾値／初期流動品の解除ロット数）は、本対策会議で具体値を確定する（決め事）。</t>
         </is>
@@ -1703,7 +1640,7 @@
       <c r="B8" s="4" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>■ 出荷判定の運用（歯止め）</t>
         </is>
@@ -1731,91 +1668,91 @@
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>監視項目</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>APHA（全項目規格）＋UV450nm（早期判定の主指標）＋UV330nm（補助）。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>監視期間</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>タンク保管中の経時を確認（必要日数は本会議で確定。UV450は実績上1日後から傾きで判別可）。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>合格基準</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>全項目が規格内、かつUV450nmの日次の傾きが基準内（傾き上限・累積ΔAPHAの具体値は本会議で確定）。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>出荷可否の承認</t>
         </is>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>確認結果に基づき出荷可否を判断（承認の担当・手順は本会議で確定）。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>出荷停止トリガー</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>初期流動品が規格内でも、その後UV450の傾きが基準を超えたら出荷停止。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>在庫回収の範囲</t>
         </is>
       </c>
-      <c r="B17" s="19" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>停止時の対象ロット範囲をあらかじめ規定（本会議で確定）。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>早期判定の保険</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>UV450単独に依らず、全項目規格内を必須とし保守的マージンを併用（偽陰性対策）。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>■ 残論点（要確認）</t>
         </is>
@@ -1835,60 +1772,60 @@
       </c>
     </row>
     <row r="21" ht="38" customHeight="1">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>メカニズムのベンチ再現</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>アルデヒド添加だけではDEGの450nmが再現できていない。タンク長期保管・低水分・塩基などの条件併存を含め、再現性の確認が必要。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="38" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>リン酸の効き方</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>pH低下で縮合を抑えるのか、金属不活性化なのか。C-1503充填部のリン到達（壁面のリン分析）で切り分け。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="38" customHeight="1">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>水分の寄与度</t>
         </is>
       </c>
-      <c r="B23" s="19" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>縮合への水分の効きは感度2〜3割の見立て。リボイラー穴の影響を除いた水分時系列（3期）で再評価する。</t>
         </is>
       </c>
     </row>
     <row r="24" ht="38" customHeight="1">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>着色物質のN分</t>
         </is>
       </c>
-      <c r="B24" s="19" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>GPC/GC-MSでN分含有の示唆。過去のアミン由来とは分子量が異なるが、N種の関与有無は要確認。</t>
         </is>
       </c>
     </row>
     <row r="25" ht="38" customHeight="1">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>前駆体の定量</t>
         </is>
       </c>
-      <c r="B25" s="19" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>前駆体・着色物質はppbオーダーで定量が困難。早期判定はUV系に絞る。</t>
         </is>

--- a/outputs/製品DEG色相悪化_事実整理.xlsx
+++ b/outputs/製品DEG色相悪化_事実整理.xlsx
@@ -13,6 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設備・開放" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="対応" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品質管理・残論点" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="候補の全整理" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="採用後（ブラッシュアップ）" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -98,8 +100,20 @@
       <color rgb="00005BAB"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <color rgb="001F7A1F"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <color rgb="00B03030"/>
+      <sz val="10.5"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -134,6 +148,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00005BAB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3D9D4"/>
       </patternFill>
     </fill>
   </fills>
@@ -207,7 +226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -269,6 +288,21 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -865,12 +899,12 @@
       <c r="B8" s="12" t="inlineStr"/>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>水和反応でEGを生成。ここでアルデヒドがグリコールと共存し始める。</t>
+          <t>水和反応でEGを生成。ここはまだ水が多く、アルドール縮合は進みにくい。アルデヒドは主に遊離のままグリコールと共存して運ばれる。</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>アルデヒドの大半は蒸気側からパージで系外へ。軽いアルデヒドは抜けるが、一部は下流へ持ち込まれ得る。</t>
+          <t>水が多い環境では縮合は進みにくい。アルデヒドの大半は蒸気側からパージで系外へ抜け、一部は遊離のまま下流へ持ち込まれ得る。</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -922,7 +956,7 @@
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>活性金属がなく、着色の生成場ではない。C-1502の見かけの生成は循環由来で通過点（要追検証）。</t>
+          <t>活性金属がなく、着色の生成場ではない。C-1502の見かけの生成は循環由来で通過点（要追検証）。温度を下げるとアルデヒド・前駆体が分解されず下流（DEG）へ回りやすい。</t>
         </is>
       </c>
       <c r="G9" s="13" t="inlineStr">
@@ -953,7 +987,7 @@
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>触媒劣化で増えたアルデヒドが、脱水以降の塔（元々水が少ない）と塩基条件のもとで縮合して重い前駆体になり、樹脂のないDEG留分を通って製品タンクへ。窒素タンクの長期保管で前駆体どうしが脱水縮合して共役が伸び、ppbオーダーで450nm＝黄色に着色する。前駆体を使い切るとAPHA30で頭打ち。</t>
+          <t>触媒劣化で増えたアルデヒドは、水が多いEG反応〜濃縮では遊離のまま運ばれ、水が抜ける脱水以降と塩基条件のもとで縮合して重い前駆体になる（MEG塔の温度を下げたことも、前駆体を分解させず下流へ回す側に働いた）。樹脂のないDEG留分を通って製品タンクへ運ばれ、窒素タンクの長期保管で前駆体どうしが脱水縮合して共役が伸び、ppbオーダーで450nm＝黄色に着色する。前駆体を使い切るとAPHA30で頭打ち。</t>
         </is>
       </c>
       <c r="B12" s="3" t="n"/>
@@ -1132,7 +1166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1150,7 +1184,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>脱水以降の塔は元々水分が少なく、アルデヒドが多いと縮合が進みやすい。脱水のプロセスを変えたわけではなく、今回はアルデヒドが多かったことが引き金で、塩基条件とDEG特有の事情が重なった。</t>
+          <t>EG反応から脱水の手前までは水が多く、アルドール縮合は進みにくい（アルデヒドは主に遊離のまま運ばれる）。水が抜ける脱水塔以降で初めて縮合が進む。脱水のプロセスを変えたわけではなく、今回はアルデヒドが多かったことが引き金で、温度操作・塩基条件・DEG特有の事情が重なった。</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -1193,32 +1227,49 @@
     <row r="5" ht="46" customHeight="1">
       <c r="A5" s="17" t="inlineStr">
         <is>
-          <t>塩基条件（苛性ソーダ）が縮合を後押しした（促進）</t>
+          <t>MEG-HUV対策で塔温度を下げたことが重なった（促進）</t>
         </is>
       </c>
       <c r="B5" s="18" t="inlineStr">
         <is>
-          <t>NaOHの塩基がアルドール縮合を促進する側に働いた（NaOHからリン酸Naへ切替で330nmが低下した実績と整合）。</t>
+          <t>温度を下げると、本来は熱で分解されるアルデヒド・前駆体が分解されずに重い形で下流（DEG）へ回る。MEG-HUVは改善したが、DEG色相は数日遅れて悪化した（時差）。</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>→ スタートアップ時はNaOH非投入</t>
+          <t>→ スタートアップ時はMEG塔温度を下げない</t>
         </is>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1">
       <c r="A6" s="17" t="inlineStr">
         <is>
+          <t>塩基条件（苛性ソーダ）が縮合を後押しした（促進）</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>NaOHの塩基がアルドール縮合を促進する側に働いた（NaOHからリン酸Naへ切替で330nmが低下した実績と整合）。</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>→ スタートアップ時はNaOH非投入</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
           <t>DEG留分には樹脂（IER）が無い（DEG特有の事情）</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>MEG・TEGはイオン交換樹脂で前駆体を除去して製品を安定化できるが、DEG留分には樹脂が無く、前駆体がそのまま製品に残る。</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>→ 出口でDEGラインのIERを検討</t>
         </is>
@@ -1846,4 +1897,696 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>これまでの議論で出た候補（全部）　採用＝淡緑／不採用＝淡赤</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>項目（仮説・観測・候補）</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>採否</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>アルドール縮合→前駆体→タンク熟成で450nm</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>アルデヒドが縮合して前駆体になり、タンクで共役が伸びて黄色に。</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>採用（主筋）</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>GPC・GCでポリエナール確定。酸素で止まる・APHA30で頭打ちの事実と整合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>水が多い上流では縮合が進みにくい</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>EG反応〜濃縮は水が多く、アルデヒドは遊離のまま運ばれる。</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>採用（条件）</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>アルドールは脱水反応。水が抜ける脱水以降で縮合が進む。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>低水分が縮合を後押し</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>脱水以降は水が少なく縮合が進む。</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>採用（条件）</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>基礎研の見立てで水分感度2〜3割。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>塩基（苛性ソーダ）がアルドールを促進</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>NaOHでアルドール縮合が進む。</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>採用（条件）</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>NaOH→リン酸Na切替で330nm低下と整合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>温度ダウンが前駆体を下流へ回す</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>温度を下げると分解されず重い形でDEGへ。</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>採用（条件）</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>MEG-HUV改善とDEG悪化の時差と整合。対応＝温度を下げない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>DEG留分に樹脂（IER）が無い</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>MEG/TEGはIERで除去、DEGは無い。</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>採用（条件）</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>DEG特有。前駆体がそのまま製品に残る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>塔間循環でC-1502に見かけ生成</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>重い縮合物が循環して上で検出される。</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>採用（解釈）</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>収支と整合。ただし要追検証。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>リン酸の緩和（pH低下／金属不活性化）</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>保管中の反応を抑える。</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>採用（緩和・要検証）</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>効き方はC-1503壁面のP分析で切り分け。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>UV450nmで早期判定</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>悪化品は約0.004/日、正常品は不動。</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>採用（指標）</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>T-604実績。APHAより早く判別。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>鉄サビが450nmの触媒</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>活性鉄が着色を促進する。</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>不採用（副次）</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="inlineStr">
+        <is>
+          <t>付着物＋DEGは380nmのみ・残液APHA30で頭打ち＝触媒でない。局所380nmに限定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>アセタール化で重質化しDEGまで輸送（HEME/開鎖）</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>アルデヒドがアセタールで高沸点化して運ばれる。</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>不採用</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="inlineStr">
+        <is>
+          <t>環状アセタールは沸点82℃で揮発し反証。縮合体としての高沸点化に一本化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>鉄＋酸素のラジカル重合で着色</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>鉄サビと酸素で重合して着色する。</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>不採用</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>酸素で止まる事実と逆（ラジカルは酸素が開始剤）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>アクロレインが着色指標</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>F+A交差でアクロレインが生成。</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>不採用（指標にせず）</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>アクロレイン濃度とAPHAは非相関。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>アミン（清缶剤由来）が原因</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>過去2回（2022/2024）の原因。</t>
+        </is>
+      </c>
+      <c r="C16" s="27" t="inlineStr">
+        <is>
+          <t>不採用（今回は別）</t>
+        </is>
+      </c>
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>今回はアミンが低い。分子量が過去と異なる。N分は残論点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>DEG/TEGがペルオキシ酸化で分解しアルデヒド生成（社外）</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>別のアルデヒド生成源の説。</t>
+        </is>
+      </c>
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t>不採用</t>
+        </is>
+      </c>
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>社外資料・基礎研『可能性2』だが主因には量的根拠不足。主筋に非中核。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>トータルアルデヒドで監視</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>アルデヒド総量で早期判定する。</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>不採用</t>
+        </is>
+      </c>
+      <c r="D18" s="26" t="inlineStr">
+        <is>
+          <t>共役アルデヒドを捉えにくく相関が弱い。UV系に絞る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>リボイラー穴で水分を誤認していた</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>2025/10頃の穴で水分が高めに見えていた。</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>採用（注記）</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>水分時系列の解釈に影響。修理後は10ppm台。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ブラッシュアップ後＝採用した筋だけを残したもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>項目（仮説・観測・候補）</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>採否</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>アルドール縮合→前駆体→タンク熟成で450nm</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>アルデヒドが縮合して前駆体になり、タンクで共役が伸びて黄色に。</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>採用（主筋）</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>GPC・GCでポリエナール確定。酸素で止まる・APHA30で頭打ちの事実と整合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>水が多い上流では縮合が進みにくい</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>EG反応〜濃縮は水が多く、アルデヒドは遊離のまま運ばれる。</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>採用（条件）</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>アルドールは脱水反応。水が抜ける脱水以降で縮合が進む。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>低水分が縮合を後押し</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>脱水以降は水が少なく縮合が進む。</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>採用（条件）</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>基礎研の見立てで水分感度2〜3割。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>塩基（苛性ソーダ）がアルドールを促進</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>NaOHでアルドール縮合が進む。</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>採用（条件）</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>NaOH→リン酸Na切替で330nm低下と整合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>温度ダウンが前駆体を下流へ回す</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>温度を下げると分解されず重い形でDEGへ。</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>採用（条件）</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>MEG-HUV改善とDEG悪化の時差と整合。対応＝温度を下げない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>DEG留分に樹脂（IER）が無い</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>MEG/TEGはIERで除去、DEGは無い。</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>採用（条件）</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>DEG特有。前駆体がそのまま製品に残る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>塔間循環でC-1502に見かけ生成</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>重い縮合物が循環して上で検出される。</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>採用（解釈）</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>収支と整合。ただし要追検証。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>リン酸の緩和（pH低下／金属不活性化）</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>保管中の反応を抑える。</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>採用（緩和・要検証）</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>効き方はC-1503壁面のP分析で切り分け。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>UV450nmで早期判定</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>悪化品は約0.004/日、正常品は不動。</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>採用（指標）</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>T-604実績。APHAより早く判別。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>リボイラー穴で水分を誤認していた</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>2025/10頃の穴で水分が高めに見えていた。</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>採用（注記）</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>水分時系列の解釈に影響。修理後は10ppm台。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>